--- a/ig/ch-elm/ValueSet-ch-elm-results-completion-vs.xlsx
+++ b/ig/ch-elm/ValueSet-ch-elm-results-completion-vs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="61">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.13.1</t>
+    <t>1.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T11:21:00+00:00</t>
+    <t>2026-05-26T14:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -105,15 +105,9 @@
     <t>Concept</t>
   </si>
   <si>
-    <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-bot-spec</t>
-  </si>
-  <si>
     <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-complete-spec</t>
   </si>
   <si>
-    <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-diph-spec</t>
-  </si>
-  <si>
     <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-geni-spec</t>
   </si>
   <si>
@@ -123,18 +117,9 @@
     <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-sterile-spec</t>
   </si>
   <si>
-    <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-tub-spec</t>
-  </si>
-  <si>
-    <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-bot-org</t>
-  </si>
-  <si>
     <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-bru-org</t>
   </si>
   <si>
-    <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-camp-diar-org</t>
-  </si>
-  <si>
     <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-camp-org</t>
   </si>
   <si>
@@ -147,12 +132,6 @@
     <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-diph-org</t>
   </si>
   <si>
-    <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-ebol-org</t>
-  </si>
-  <si>
-    <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-ehec-org</t>
-  </si>
-  <si>
     <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-ehec-tox-org</t>
   </si>
   <si>
@@ -162,12 +141,6 @@
     <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-hanta-org</t>
   </si>
   <si>
-    <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-hiv-org</t>
-  </si>
-  <si>
-    <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-inf-org</t>
-  </si>
-  <si>
     <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-influenza-hxny-org</t>
   </si>
   <si>
@@ -192,15 +165,6 @@
     <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-mpox-org</t>
   </si>
   <si>
-    <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-mpx-ctng</t>
-  </si>
-  <si>
-    <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-mpx-sash</t>
-  </si>
-  <si>
-    <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-mpx-sashec</t>
-  </si>
-  <si>
     <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-pneu-org</t>
   </si>
   <si>
@@ -210,10 +174,10 @@
     <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-sal-org-complete</t>
   </si>
   <si>
+    <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-shi-nent-org</t>
+  </si>
+  <si>
     <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-shi-org</t>
-  </si>
-  <si>
-    <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-tub-gen-org</t>
   </si>
   <si>
     <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-tub-org</t>
@@ -497,7 +461,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -684,88 +648,16 @@
       <c r="A30" t="s" s="2">
         <v>58</v>
       </c>
-      <c r="B30" s="2"/>
+      <c r="B30" t="s" s="2">
+        <v>58</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
         <v>59</v>
       </c>
-      <c r="B31" s="2"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="s" s="2">
+      <c r="B31" t="s" s="2">
         <v>60</v>
-      </c>
-      <c r="B32" s="2"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="B33" s="2"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="B34" s="2"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="B35" s="2"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="B36" s="2"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="B37" s="2"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="B38" s="2"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="B39" s="2"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="B40" s="2"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="B41" s="2"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="B42" t="s" s="2">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/ig/ch-elm/ValueSet-ch-elm-results-completion-vs.xlsx
+++ b/ig/ch-elm/ValueSet-ch-elm-results-completion-vs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="60">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.0</t>
+    <t>1.14.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T14:58:40+00:00</t>
+    <t>2026-07-01T19:23:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -130,9 +130,6 @@
   </si>
   <si>
     <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-diph-org</t>
-  </si>
-  <si>
-    <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-ehec-tox-org</t>
   </si>
   <si>
     <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-haem-org</t>
@@ -461,7 +458,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -642,22 +639,16 @@
       <c r="A29" t="s" s="2">
         <v>57</v>
       </c>
-      <c r="B29" s="2"/>
+      <c r="B29" t="s" s="2">
+        <v>57</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
         <v>58</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s" s="2">
         <v>59</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/ig/ch-elm/ValueSet-ch-elm-results-completion-vs.xlsx
+++ b/ig/ch-elm/ValueSet-ch-elm-results-completion-vs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.1</t>
+    <t>1.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T19:23:08+00:00</t>
+    <t>2026-08-12T07:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/ValueSet-ch-elm-results-completion-vs.xlsx
+++ b/ig/ch-elm/ValueSet-ch-elm-results-completion-vs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.15.0</t>
+    <t>1.15.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T07:20:00+00:00</t>
+    <t>2026-08-14T07:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
